--- a/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461A8DE4-79D0-4691-B457-FB7659802252}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B71E35-7E12-40C1-BF2C-3983FAA48276}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JUNE" sheetId="902" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="92">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -356,6 +356,18 @@
   </si>
   <si>
     <t>9/3B</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>13/12B</t>
+  </si>
+  <si>
+    <t>2/3B</t>
+  </si>
+  <si>
+    <t>12/3B</t>
   </si>
 </sst>
 </file>
@@ -976,7 +988,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1223,6 +1235,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3084,47 +3100,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3356,12 +3372,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4690,47 +4706,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -4962,12 +4978,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -5003,17 +5019,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6312,47 +6328,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6584,12 +6600,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6625,17 +6641,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7934,47 +7950,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8206,12 +8222,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8247,20 +8263,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+1+26+15+15+3+5+62+2+10+551</f>
         <v>691</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9557,47 +9573,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -9829,12 +9845,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11163,47 +11179,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11435,12 +11451,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11476,17 +11492,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12785,47 +12801,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13057,12 +13073,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -13098,17 +13114,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14407,47 +14423,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -14679,12 +14695,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -14720,20 +14736,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+1+26+15+15+3+5+62+2+10+551</f>
         <v>691</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -16030,47 +16046,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16302,12 +16318,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -17636,47 +17652,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -17908,12 +17924,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -17949,17 +17965,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19256,47 +19272,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -19528,12 +19544,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -20860,47 +20876,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21132,12 +21148,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21173,17 +21189,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -22482,47 +22498,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -22754,12 +22770,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -22795,20 +22811,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+1+26+15+15+3+5+62+2+10+551</f>
         <v>691</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -24105,47 +24121,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -24377,12 +24393,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -25711,47 +25727,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -25983,12 +25999,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26024,17 +26040,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -27333,47 +27349,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -27605,12 +27621,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -27646,17 +27662,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -28955,47 +28971,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -29227,12 +29243,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -29268,20 +29284,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+1+26+15+15+3+5+62+2+10+551</f>
         <v>691</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -30578,47 +30594,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -30850,12 +30866,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -32184,47 +32200,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -32456,12 +32472,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -32497,17 +32513,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -33806,47 +33822,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -34078,12 +34094,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -34119,17 +34135,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -35428,47 +35444,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -35700,12 +35716,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -35741,20 +35757,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+1+26+15+15+3+5+62+2+10+551</f>
         <v>691</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -37116,47 +37132,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -37436,12 +37452,12 @@
       <c r="Q42" s="43">
         <v>19</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -37477,23 +37493,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>2+6+10+10+13+10+570</f>
         <v>621</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <f>22+12+1</f>
         <v>35</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -38864,47 +38880,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -39176,12 +39192,12 @@
       <c r="Q42" s="43">
         <v>3</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -39217,22 +39233,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>1+3+1+1+40+6+275</f>
         <v>327</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="92">
         <v>12</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -40597,47 +40613,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -40905,12 +40921,12 @@
       <c r="Q42" s="43">
         <v>13</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -40946,20 +40962,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="92">
         <f>10+2+3+1+25+6+307</f>
         <v>354</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -42256,47 +42272,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -42528,12 +42544,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -42591,7 +42607,8 @@
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
     <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -42960,12 +42977,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -42977,11 +42998,17 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -43148,12 +43175,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>11</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -43165,23 +43196,33 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>88</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -43193,11 +43234,17 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -43600,14 +43647,24 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>341</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -43786,14 +43843,24 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>9</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>8</v>
+      </c>
+      <c r="M31" s="23">
+        <v>37</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -43814,14 +43881,24 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>11</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>304</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -43862,47 +43939,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -43963,19 +44040,35 @@
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="E36" s="42">
+        <v>23</v>
+      </c>
+      <c r="F36" s="42">
+        <v>312</v>
+      </c>
+      <c r="G36" s="42">
+        <v>5</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>2</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="M36" s="42">
+        <v>2</v>
+      </c>
+      <c r="N36" s="42">
+        <v>1</v>
+      </c>
+      <c r="O36" s="42">
+        <v>1</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>6</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -44121,25 +44214,41 @@
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="E42" s="42">
+        <v>23</v>
+      </c>
+      <c r="F42" s="42">
+        <v>312</v>
+      </c>
+      <c r="G42" s="42">
+        <v>5</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>2</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="M42" s="42">
+        <v>2</v>
+      </c>
+      <c r="N42" s="42">
+        <v>1</v>
+      </c>
+      <c r="O42" s="42">
+        <v>1</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="Q42" s="43">
+        <v>6</v>
+      </c>
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -44175,17 +44284,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92">
+        <f>1+1+11+2+304</f>
+        <v>319</v>
+      </c>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92">
+        <v>12</v>
+      </c>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -44213,7 +44327,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -44582,12 +44697,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="78"/>
+      <c r="C8" s="80">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -44599,11 +44718,17 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -44770,12 +44895,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>88</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -44787,23 +44916,33 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>13</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -44815,11 +44954,17 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -45222,17 +45367,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>24</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L24" s="14">
+        <v>6</v>
+      </c>
+      <c r="M24" s="14">
+        <v>411</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -45408,17 +45565,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>88</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>23</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L31" s="23">
+        <v>6</v>
+      </c>
+      <c r="M31" s="23">
+        <v>81</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>86</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -45436,17 +45605,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>1</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <v>330</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -45484,47 +45665,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -45583,10 +45764,14 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>334</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
@@ -45595,9 +45780,15 @@
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
+      <c r="P36" s="42">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>2</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -45741,10 +45932,14 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>334</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
@@ -45753,15 +45948,21 @@
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
+      <c r="P42" s="42">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>2</v>
+      </c>
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -45797,17 +45998,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92">
+        <f>13+1+1+330</f>
+        <v>345</v>
+      </c>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -46204,29 +46408,63 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
+      <c r="C8" s="13">
+        <v>11</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>5</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>5</v>
+      </c>
+      <c r="I8" s="14">
+        <v>1</v>
+      </c>
       <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="K8" s="14">
+        <v>1</v>
+      </c>
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
+      <c r="N8" s="14">
+        <v>1</v>
+      </c>
+      <c r="O8" s="14">
+        <v>1</v>
+      </c>
+      <c r="P8" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>1</v>
+      </c>
       <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="S8" s="14">
+        <v>1</v>
+      </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="V8" s="14">
+        <v>2</v>
+      </c>
+      <c r="W8" s="14">
+        <v>10</v>
+      </c>
+      <c r="X8" s="59">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -46392,57 +46630,125 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>4</v>
+      </c>
+      <c r="I15" s="23">
+        <v>0</v>
+      </c>
       <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
+      <c r="K15" s="23">
+        <v>0</v>
+      </c>
       <c r="L15" s="23"/>
       <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
+      <c r="N15" s="23">
+        <v>0</v>
+      </c>
+      <c r="O15" s="23">
+        <v>0</v>
+      </c>
+      <c r="P15" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>0</v>
+      </c>
       <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
+      <c r="S15" s="23">
+        <v>0</v>
+      </c>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="V15" s="23">
+        <v>0</v>
+      </c>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
+      <c r="C16" s="57">
+        <v>10</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>5</v>
+      </c>
+      <c r="F16" s="27">
+        <v>2</v>
+      </c>
+      <c r="G16" s="28">
+        <v>5</v>
+      </c>
+      <c r="H16" s="28">
+        <v>1</v>
+      </c>
+      <c r="I16" s="28">
+        <v>1</v>
+      </c>
       <c r="J16" s="28"/>
-      <c r="K16" s="56"/>
+      <c r="K16" s="56">
+        <v>1</v>
+      </c>
       <c r="L16" s="28"/>
       <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
+      <c r="N16" s="28">
+        <v>1</v>
+      </c>
+      <c r="O16" s="28">
+        <v>1</v>
+      </c>
+      <c r="P16" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="28">
+        <v>1</v>
+      </c>
       <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
+      <c r="S16" s="28">
+        <v>1</v>
+      </c>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
-      <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="V16" s="28">
+        <v>2</v>
+      </c>
+      <c r="W16" s="56">
+        <v>10</v>
+      </c>
+      <c r="X16" s="62">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -46842,25 +47148,51 @@
         <v>23</v>
       </c>
       <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="D24" s="14">
+        <v>2</v>
+      </c>
+      <c r="E24" s="14">
+        <v>2</v>
+      </c>
+      <c r="F24" s="14">
+        <v>7</v>
+      </c>
+      <c r="G24" s="14">
+        <v>1</v>
+      </c>
+      <c r="H24" s="14">
+        <v>102</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>348</v>
+      </c>
+      <c r="N24" s="14">
+        <v>1</v>
+      </c>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
+      <c r="R24" s="14">
+        <v>1</v>
+      </c>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
+      <c r="U24" s="14">
+        <v>1</v>
+      </c>
+      <c r="V24" s="14">
+        <v>1</v>
+      </c>
       <c r="W24" s="14"/>
       <c r="X24" s="14"/>
       <c r="Y24" s="15"/>
@@ -47028,25 +47360,51 @@
         <v>25</v>
       </c>
       <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="D31" s="23">
+        <v>0</v>
+      </c>
+      <c r="E31" s="23">
+        <v>0</v>
+      </c>
+      <c r="F31" s="23">
+        <v>7</v>
+      </c>
+      <c r="G31" s="23">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23">
+        <v>28</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>2</v>
+      </c>
+      <c r="N31" s="23">
+        <v>0</v>
+      </c>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
+      <c r="R31" s="23">
+        <v>0</v>
+      </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="U31" s="23">
+        <v>0</v>
+      </c>
+      <c r="V31" s="23">
+        <v>0</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="61"/>
       <c r="Y31" s="24"/>
@@ -47056,25 +47414,51 @@
         <v>26</v>
       </c>
       <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="D32" s="27">
+        <v>2</v>
+      </c>
+      <c r="E32" s="27">
+        <v>2</v>
+      </c>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
+      <c r="G32" s="28">
+        <v>1</v>
+      </c>
+      <c r="H32" s="28">
+        <v>74</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>20</v>
+      </c>
+      <c r="M32" s="28">
+        <v>346</v>
+      </c>
+      <c r="N32" s="28">
+        <v>1</v>
+      </c>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>10</v>
+      </c>
       <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
+      <c r="R32" s="28">
+        <v>1</v>
+      </c>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="U32" s="28">
+        <v>1</v>
+      </c>
+      <c r="V32" s="28">
+        <v>1</v>
+      </c>
       <c r="W32" s="28"/>
       <c r="X32" s="63"/>
       <c r="Y32" s="29"/>
@@ -47106,47 +47490,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="88"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="88"/>
+      <c r="N34" s="89"/>
+      <c r="O34" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="83"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -47205,21 +47589,45 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
+      <c r="D36" s="41">
+        <v>7</v>
+      </c>
+      <c r="E36" s="42">
+        <v>11</v>
+      </c>
+      <c r="F36" s="42">
+        <v>278</v>
+      </c>
+      <c r="G36" s="42">
+        <v>382</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
       <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
+      <c r="J36" s="42">
+        <v>32</v>
+      </c>
+      <c r="K36" s="42">
+        <v>7</v>
+      </c>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42">
+        <v>69</v>
+      </c>
+      <c r="N36" s="42">
+        <v>10</v>
+      </c>
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>5</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -47363,27 +47771,51 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
+      <c r="D42" s="41">
+        <v>7</v>
+      </c>
+      <c r="E42" s="42">
+        <v>11</v>
+      </c>
+      <c r="F42" s="42">
+        <v>278</v>
+      </c>
+      <c r="G42" s="42">
+        <v>382</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
       <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
+      <c r="J42" s="42">
+        <v>32</v>
+      </c>
+      <c r="K42" s="42">
+        <v>7</v>
+      </c>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42">
+        <v>69</v>
+      </c>
+      <c r="N42" s="42">
+        <v>10</v>
+      </c>
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="Q42" s="43">
+        <v>5</v>
+      </c>
+      <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -47419,20 +47851,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
-        <f>1+1+26+15+15+3+5+62+2+10+551</f>
-        <v>691</v>
-      </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="92">
+        <f>10+5+2+5+1+1+1+1+1+1+1+1+2+10+10+2+2+2+1+74+1+20+346+1+10+1+1+1</f>
+        <v>514</v>
+      </c>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B71E35-7E12-40C1-BF2C-3983FAA48276}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E10AB9-7614-4FC3-B0C0-FF1CA00911D8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JUNE" sheetId="902" r:id="rId1"/>

--- a/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E10AB9-7614-4FC3-B0C0-FF1CA00911D8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686730C4-46F8-4CED-9926-B3CBA72C0767}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JUNE" sheetId="902" r:id="rId1"/>
@@ -24,8 +24,8 @@
     <sheet name="06-02 R3" sheetId="1726" r:id="rId9"/>
     <sheet name="(3)" sheetId="1727" r:id="rId10"/>
     <sheet name="06-03 R1" sheetId="1728" r:id="rId11"/>
-    <sheet name="06-03 R2" sheetId="1729" r:id="rId12"/>
-    <sheet name="06-03 R3" sheetId="1730" r:id="rId13"/>
+    <sheet name="06-03 R2 NO TRIP" sheetId="1729" r:id="rId12"/>
+    <sheet name="06-03 R3 NO TRIP" sheetId="1730" r:id="rId13"/>
     <sheet name="(4)" sheetId="1731" r:id="rId14"/>
     <sheet name="06-04 R1" sheetId="1732" r:id="rId15"/>
     <sheet name="06-04 R2" sheetId="1733" r:id="rId16"/>
@@ -61,8 +61,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'06-02 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'06-02 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'06-03 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'06-03 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'06-03 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'06-03 R2 NO TRIP'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'06-03 R3 NO TRIP'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'06-04 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'06-04 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'06-04 R3'!$A$1:$V$44</definedName>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="93">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>12/3B</t>
+  </si>
+  <si>
+    <t>15/12B</t>
   </si>
 </sst>
 </file>
@@ -3435,7 +3438,8 @@
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
     <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -3805,11 +3809,19 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -3821,10 +3833,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -3993,11 +4009,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>2</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -4009,10 +4033,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -4021,11 +4049,19 @@
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="D16" s="58">
+        <v>2</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>89</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -4037,10 +4073,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>2</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>2</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -4444,17 +4484,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>10</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>5</v>
+      </c>
+      <c r="M24" s="14">
+        <v>443</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>8</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -4630,17 +4682,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>2</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>6</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -4658,17 +4722,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>10</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>5</v>
+      </c>
+      <c r="M32" s="28">
+        <v>441</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>2</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -4808,18 +4884,36 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>351</v>
+      </c>
+      <c r="G36" s="42">
+        <v>12</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>5</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="42">
+        <v>6</v>
+      </c>
+      <c r="L36" s="42">
+        <v>8</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>1</v>
+      </c>
+      <c r="P36" s="42">
+        <v>7</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>11</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -4966,18 +5060,36 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>351</v>
+      </c>
+      <c r="G42" s="42">
+        <v>12</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>5</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="K42" s="42">
+        <v>6</v>
+      </c>
+      <c r="L42" s="42">
+        <v>8</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>1</v>
+      </c>
+      <c r="P42" s="42">
+        <v>7</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>11</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -5019,7 +5131,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>2+1+1+13+2+2+1+10+1+5+441+2</f>
+        <v>481</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -5027,7 +5142,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="92">
+        <f>12</f>
+        <v>12</v>
+      </c>
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
     </row>

--- a/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686730C4-46F8-4CED-9926-B3CBA72C0767}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2940EA26-FA11-4B14-8EF2-0FA8C16922A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="10" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="16" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JUNE" sheetId="902" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="94">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>15/12B</t>
+  </si>
+  <si>
+    <t>10/12B</t>
   </si>
 </sst>
 </file>
@@ -10026,7 +10029,8 @@
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
     <col min="3" max="5" width="5.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -10395,12 +10399,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>21</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -10412,11 +10420,17 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>27</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -10583,12 +10597,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>93</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -10600,23 +10618,33 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>93</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -10628,11 +10656,17 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>26</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -11035,17 +11069,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>127</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>66</v>
+      </c>
+      <c r="L24" s="14">
+        <v>58</v>
+      </c>
+      <c r="M24" s="14">
+        <v>399</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>6</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -11221,17 +11267,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>10</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>8</v>
+      </c>
+      <c r="M31" s="23">
+        <v>29</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>3</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -11249,17 +11307,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>117</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>65</v>
+      </c>
+      <c r="L32" s="28">
+        <v>50</v>
+      </c>
+      <c r="M32" s="28">
+        <v>370</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>3</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -11399,16 +11469,30 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="F36" s="42">
+        <v>553</v>
+      </c>
+      <c r="G36" s="42">
+        <v>7</v>
+      </c>
+      <c r="H36" s="42">
+        <v>11</v>
+      </c>
+      <c r="I36" s="42">
+        <v>50</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="42">
+        <v>9</v>
+      </c>
+      <c r="L36" s="42">
+        <v>68</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>12</v>
+      </c>
       <c r="P36" s="42"/>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
@@ -11557,16 +11641,30 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="F42" s="42">
+        <v>553</v>
+      </c>
+      <c r="G42" s="42">
+        <v>7</v>
+      </c>
+      <c r="H42" s="42">
+        <v>11</v>
+      </c>
+      <c r="I42" s="42">
+        <v>50</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="K42" s="42">
+        <v>9</v>
+      </c>
+      <c r="L42" s="42">
+        <v>68</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>12</v>
+      </c>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
       <c r="R42" s="84" t="s">
@@ -11610,7 +11708,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>10+26+117+65+50+370</f>
+        <v>638</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -11618,7 +11719,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="92">
+        <v>12</v>
+      </c>
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
     </row>

--- a/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2940EA26-FA11-4B14-8EF2-0FA8C16922A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7484DA-9843-4E97-A621-45232BD42143}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="16" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="94">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -11642,7 +11642,7 @@
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
       <c r="F42" s="42">
-        <v>553</v>
+        <v>603</v>
       </c>
       <c r="G42" s="42">
         <v>7</v>
@@ -12120,12 +12120,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="78"/>
+      <c r="C8" s="80">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>10</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -12140,8 +12148,12 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -12308,12 +12320,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>3</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -12328,8 +12348,12 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -12338,10 +12362,16 @@
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>2</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>7</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -12356,8 +12386,12 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -12760,17 +12794,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>23</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L24" s="14">
+        <v>6</v>
+      </c>
+      <c r="M24" s="14">
+        <v>387</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -12946,17 +12992,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>85</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L31" s="23">
+        <v>5</v>
+      </c>
+      <c r="M31" s="23">
+        <v>90</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>86</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -12974,14 +13032,24 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>23</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>1</v>
+      </c>
+      <c r="M32" s="28">
+        <v>297</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -13121,21 +13189,43 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>2</v>
+      </c>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="E36" s="42">
+        <v>1</v>
+      </c>
+      <c r="F36" s="42">
+        <v>353</v>
+      </c>
+      <c r="G36" s="42">
+        <v>9</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>5</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="K36" s="42">
+        <v>3</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="N36" s="42">
+        <v>1</v>
+      </c>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
+      <c r="P36" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>1</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -13279,21 +13369,43 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>2</v>
+      </c>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="E42" s="42">
+        <v>1</v>
+      </c>
+      <c r="F42" s="42">
+        <v>353</v>
+      </c>
+      <c r="G42" s="42">
+        <v>9</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>5</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="K42" s="42">
+        <v>3</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="N42" s="42">
+        <v>1</v>
+      </c>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
+      <c r="P42" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>1</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -13335,7 +13447,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="92"/>
+      <c r="C44" s="92">
+        <f>2+2+7+23+1+297</f>
+        <v>332</v>
+      </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
     </row>
@@ -13742,12 +13857,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>7</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>24</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -13759,10 +13884,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>20</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>20</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -13930,12 +14059,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -13947,10 +14086,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -13960,10 +14103,16 @@
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>7</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>24</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -13975,10 +14124,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>20</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>20</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -14382,19 +14535,33 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>7</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>136</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>20</v>
+      </c>
+      <c r="M24" s="14">
+        <v>541</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
+      <c r="R24" s="14">
+        <v>1</v>
+      </c>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
@@ -14568,19 +14735,33 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>7</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>2</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
+      <c r="R31" s="23">
+        <v>0</v>
+      </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
@@ -14596,19 +14777,31 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>135</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>20</v>
+      </c>
+      <c r="M32" s="28">
+        <v>539</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
       <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
+      <c r="R32" s="28">
+        <v>1</v>
+      </c>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
@@ -14743,21 +14936,49 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="C36" s="46">
+        <v>3</v>
+      </c>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
+      <c r="E36" s="42">
+        <v>19</v>
+      </c>
+      <c r="F36" s="42">
+        <v>756</v>
+      </c>
+      <c r="G36" s="42">
+        <v>2</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>14</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>10</v>
+      </c>
+      <c r="L36" s="42">
+        <v>13</v>
+      </c>
       <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="N36" s="42">
+        <v>7</v>
+      </c>
+      <c r="O36" s="42">
+        <v>11</v>
+      </c>
+      <c r="P36" s="42">
+        <v>24</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>14</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -14901,21 +15122,49 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="C42" s="46">
+        <v>3</v>
+      </c>
+      <c r="D42" s="41">
+        <v>1</v>
+      </c>
+      <c r="E42" s="42">
+        <v>19</v>
+      </c>
+      <c r="F42" s="42">
+        <v>756</v>
+      </c>
+      <c r="G42" s="42">
+        <v>2</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>14</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>10</v>
+      </c>
+      <c r="L42" s="42">
+        <v>13</v>
+      </c>
       <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="N42" s="42">
+        <v>7</v>
+      </c>
+      <c r="O42" s="42">
+        <v>11</v>
+      </c>
+      <c r="P42" s="42">
+        <v>24</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>14</v>
+      </c>
       <c r="R42" s="84" t="s">
         <v>54</v>
       </c>
@@ -14958,8 +15207,8 @@
         <v>68</v>
       </c>
       <c r="C44" s="92">
-        <f>1+1+26+15+15+3+5+62+2+10+551</f>
-        <v>691</v>
+        <f>2+7+24+20+20+135+20+539+1</f>
+        <v>768</v>
       </c>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>

--- a/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39271861-5FC9-4DA2-8C79-0FCA42CF9872}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA963A5-5438-4A3A-A64F-AED762687D78}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="28" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JUNE" sheetId="902" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <sheet name="06-06 R2" sheetId="1741" r:id="rId24"/>
     <sheet name="06-06 R3" sheetId="1742" r:id="rId25"/>
     <sheet name="(8)" sheetId="1743" r:id="rId26"/>
-    <sheet name="06-08 R1" sheetId="1744" r:id="rId27"/>
+    <sheet name="06-08 R1 NO TRIP" sheetId="1744" r:id="rId27"/>
     <sheet name="06-08 R2" sheetId="1745" r:id="rId28"/>
     <sheet name="06-08 R3" sheetId="1746" r:id="rId29"/>
     <sheet name="(9)" sheetId="1747" r:id="rId30"/>
@@ -82,7 +82,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="22">'06-06 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">'06-06 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="24">'06-06 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="26">'06-08 R1'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'06-08 R1 NO TRIP'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="27">'06-08 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'06-08 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="30">'06-09 R1'!$A$1:$Z$43</definedName>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="97">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>DATE ___________06/10/2026___________</t>
+  </si>
+  <si>
+    <t>20/12B</t>
   </si>
 </sst>
 </file>
@@ -33623,12 +33626,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="78"/>
+      <c r="C8" s="78">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>15</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -33643,8 +33650,12 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -33811,12 +33822,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -33831,20 +33846,28 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>15</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -33859,8 +33882,12 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -34263,17 +34290,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>50</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L24" s="14">
+        <v>8</v>
+      </c>
+      <c r="M24" s="14">
+        <v>482</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -34449,17 +34488,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>85</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>17</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L31" s="23">
+        <v>4</v>
+      </c>
+      <c r="M31" s="23">
+        <v>25</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>86</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -34477,17 +34528,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>33</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>4</v>
+      </c>
+      <c r="M32" s="28">
+        <v>457</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -34627,17 +34690,33 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="F36" s="42">
+        <v>495</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>4</v>
+      </c>
+      <c r="I36" s="42">
+        <v>3</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>8</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
+      <c r="P36" s="42">
+        <v>15</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
@@ -34785,17 +34864,33 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="F42" s="42">
+        <v>495</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>4</v>
+      </c>
+      <c r="I42" s="42">
+        <v>3</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>8</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
+      <c r="P42" s="42">
+        <v>15</v>
+      </c>
       <c r="Q42" s="43"/>
       <c r="R42" s="85" t="s">
         <v>54</v>
@@ -34838,7 +34933,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
+      <c r="C44" s="93">
+        <f>15+33+4+457</f>
+        <v>509</v>
+      </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
     </row>
@@ -34876,7 +34974,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -35245,12 +35344,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -35262,10 +35367,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>5</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -35433,12 +35542,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>10</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -35450,10 +35565,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -35461,12 +35580,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>93</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -35478,10 +35603,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>1</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>5</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -35885,17 +36014,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>5</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>77</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>16</v>
+      </c>
+      <c r="M24" s="14">
+        <v>477</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -36071,17 +36212,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>5</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>6</v>
+      </c>
+      <c r="M31" s="23">
+        <v>61</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -36099,17 +36252,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>76</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28">
+        <v>416</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -36247,20 +36412,46 @@
         <v>52</v>
       </c>
       <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
+      <c r="E36" s="42">
+        <v>10</v>
+      </c>
+      <c r="F36" s="42">
+        <v>467</v>
+      </c>
+      <c r="G36" s="42">
+        <v>10</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>25</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="K36" s="42">
+        <v>33</v>
+      </c>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>8</v>
+      </c>
+      <c r="O36" s="42">
+        <v>5</v>
+      </c>
+      <c r="P36" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>7</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -36405,20 +36596,46 @@
         <v>53</v>
       </c>
       <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="D42" s="41">
+        <v>1</v>
+      </c>
+      <c r="E42" s="42">
+        <v>10</v>
+      </c>
+      <c r="F42" s="42">
+        <v>467</v>
+      </c>
+      <c r="G42" s="42">
+        <v>10</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>25</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="K42" s="42">
+        <v>33</v>
+      </c>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>8</v>
+      </c>
+      <c r="O42" s="42">
+        <v>5</v>
+      </c>
+      <c r="P42" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>7</v>
+      </c>
       <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
@@ -36461,8 +36678,8 @@
         <v>68</v>
       </c>
       <c r="C44" s="93">
-        <f>1+1+26+15+15+3+5+62+2+10+551</f>
-        <v>691</v>
+        <f>10+1+5+76+10+416</f>
+        <v>518</v>
       </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>

--- a/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/CSR MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA963A5-5438-4A3A-A64F-AED762687D78}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A745D213-D5E6-4FE6-8758-D700D090E4E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="28" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="25" activeTab="36" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | JUNE" sheetId="902" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <sheet name="06-09 R3" sheetId="1750" r:id="rId33"/>
     <sheet name="(10)" sheetId="1751" r:id="rId34"/>
     <sheet name="06-10 R1" sheetId="1752" r:id="rId35"/>
-    <sheet name="06-10 R2" sheetId="1753" r:id="rId36"/>
+    <sheet name="06-10 R2 NO TRIP" sheetId="1753" r:id="rId36"/>
     <sheet name="06-10 R3" sheetId="1754" r:id="rId37"/>
   </sheets>
   <externalReferences>
@@ -89,7 +89,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="31">'06-09 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="32">'06-09 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="34">'06-10 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="35">'06-10 R2'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="35">'06-10 R2 NO TRIP'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="36">'06-10 R3'!$A$1:$V$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="104">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -399,6 +399,27 @@
   </si>
   <si>
     <t>20/12B</t>
+  </si>
+  <si>
+    <t>2/12b</t>
+  </si>
+  <si>
+    <t>9/12b</t>
+  </si>
+  <si>
+    <t>12b</t>
+  </si>
+  <si>
+    <t>5/12b</t>
+  </si>
+  <si>
+    <t>1/12b</t>
+  </si>
+  <si>
+    <t>9/4b</t>
+  </si>
+  <si>
+    <t>9/3b</t>
   </si>
 </sst>
 </file>
@@ -40430,12 +40451,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -40446,12 +40475,18 @@
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="S8" s="14">
+        <v>1</v>
+      </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -40618,12 +40653,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>7</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -40634,24 +40677,38 @@
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
+      <c r="S15" s="23">
+        <v>1</v>
+      </c>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>2</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>97</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -40662,12 +40719,18 @@
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
+      <c r="S16" s="28">
+        <v>0</v>
+      </c>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -41070,17 +41133,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>21</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>9</v>
+      </c>
+      <c r="M24" s="14">
+        <v>385</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -41256,17 +41331,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>46</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>10</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -41284,17 +41371,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>20</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>9</v>
+      </c>
+      <c r="M32" s="28">
+        <v>339</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -41434,18 +41533,36 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="F36" s="42">
+        <v>300</v>
+      </c>
+      <c r="G36" s="42">
+        <v>6</v>
+      </c>
+      <c r="H36" s="42">
+        <v>2</v>
+      </c>
+      <c r="I36" s="42">
+        <v>8</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>2</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>1</v>
+      </c>
+      <c r="P36" s="42">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>21</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -41592,18 +41709,36 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="F42" s="42">
+        <v>300</v>
+      </c>
+      <c r="G42" s="42">
+        <v>6</v>
+      </c>
+      <c r="H42" s="42">
+        <v>2</v>
+      </c>
+      <c r="I42" s="42">
+        <v>8</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>2</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>1</v>
+      </c>
+      <c r="P42" s="42">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>21</v>
+      </c>
       <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
@@ -41645,7 +41780,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
+      <c r="C44" s="93">
+        <f>2+2+2+1+1+20+9+339</f>
+        <v>376</v>
+      </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
     </row>
@@ -41653,7 +41791,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="93"/>
+      <c r="C45" s="93">
+        <f>12</f>
+        <v>12</v>
+      </c>
       <c r="D45" s="93"/>
       <c r="E45" s="93"/>
     </row>
@@ -42052,12 +42193,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="78"/>
+      <c r="C8" s="80">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>13</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -42072,8 +42221,12 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -42240,12 +42393,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -42260,20 +42421,32 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
       <c r="Y15" s="24"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>12</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -42288,8 +42461,12 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
       <c r="Y16" s="29"/>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -42692,17 +42869,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="s">
+        <v>100</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>50</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L24" s="14">
+        <v>4</v>
+      </c>
+      <c r="M24" s="14">
+        <v>368</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>102</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -42878,17 +43067,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23" t="s">
+        <v>99</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>45</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>102</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -42906,17 +43107,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>5</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>50</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>3</v>
+      </c>
+      <c r="M32" s="28">
+        <v>323</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -43053,21 +43266,43 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>4</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="F36" s="42">
+        <v>386</v>
+      </c>
+      <c r="G36" s="42">
+        <v>9</v>
+      </c>
+      <c r="H36" s="42">
+        <v>4</v>
+      </c>
+      <c r="I36" s="42">
+        <v>3</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
+      <c r="L36" s="42">
+        <v>5</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>13</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>1</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -43211,21 +43446,43 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>4</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="F42" s="42">
+        <v>386</v>
+      </c>
+      <c r="G42" s="42">
+        <v>9</v>
+      </c>
+      <c r="H42" s="42">
+        <v>4</v>
+      </c>
+      <c r="I42" s="42">
+        <v>3</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
+      <c r="L42" s="42">
+        <v>5</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>13</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>1</v>
+      </c>
       <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
@@ -43267,7 +43524,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
+      <c r="C44" s="93">
+        <f>2+1+12+1+5+50+3+323</f>
+        <v>397</v>
+      </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
     </row>
@@ -43674,12 +43934,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>20</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -43691,12 +43957,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>7</v>
+      </c>
+      <c r="X8" s="59">
+        <v>20</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -43862,12 +44136,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -43879,23 +44159,37 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>19</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -43907,12 +44201,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>7</v>
+      </c>
+      <c r="X16" s="62">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -44314,17 +44616,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>5</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>109</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>35</v>
+      </c>
+      <c r="M24" s="14">
+        <v>493</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>103</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -44500,17 +44814,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>8</v>
+      </c>
+      <c r="M31" s="23">
+        <v>3</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>103</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -44528,17 +44854,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>5</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>108</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>27</v>
+      </c>
+      <c r="M32" s="28">
+        <v>490</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -44675,21 +45013,47 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>1</v>
+      </c>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="E36" s="42">
+        <v>24</v>
+      </c>
+      <c r="F36" s="42">
+        <v>562</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>19</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="K36" s="42">
+        <v>8</v>
+      </c>
+      <c r="L36" s="42">
+        <v>7</v>
+      </c>
+      <c r="M36" s="42">
+        <v>4</v>
+      </c>
+      <c r="N36" s="42">
+        <v>4</v>
+      </c>
+      <c r="O36" s="42">
+        <v>14</v>
+      </c>
+      <c r="P36" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>22</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -44833,21 +45197,47 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>1</v>
+      </c>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="E42" s="42">
+        <v>24</v>
+      </c>
+      <c r="F42" s="42">
+        <v>562</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>19</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="K42" s="42">
+        <v>8</v>
+      </c>
+      <c r="L42" s="42">
+        <v>7</v>
+      </c>
+      <c r="M42" s="42">
+        <v>4</v>
+      </c>
+      <c r="N42" s="42">
+        <v>4</v>
+      </c>
+      <c r="O42" s="42">
+        <v>14</v>
+      </c>
+      <c r="P42" s="42">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>22</v>
+      </c>
       <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
@@ -46903,12 +47293,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>3</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>4</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>7</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -46920,10 +47318,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -47091,12 +47493,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>7</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -47108,10 +47518,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -47119,12 +47533,20 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>2</v>
+      </c>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>4</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>0</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -47136,10 +47558,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -47543,17 +47969,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>21</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>370</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>10</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -47729,17 +48167,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>6</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>2</v>
+      </c>
+      <c r="M31" s="23">
+        <v>58</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>8</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -47757,17 +48207,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>15</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>8</v>
+      </c>
+      <c r="M32" s="28">
+        <v>312</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>2</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -47907,14 +48369,30 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
+      <c r="F36" s="42">
+        <v>321</v>
+      </c>
+      <c r="G36" s="42">
+        <v>6</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>9</v>
+      </c>
+      <c r="J36" s="42">
+        <v>4</v>
+      </c>
+      <c r="K36" s="42">
+        <v>4</v>
+      </c>
+      <c r="L36" s="42">
+        <v>2</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
       <c r="N36" s="42"/>
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
@@ -48065,14 +48543,30 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
+      <c r="F42" s="42">
+        <v>321</v>
+      </c>
+      <c r="G42" s="42">
+        <v>6</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>9</v>
+      </c>
+      <c r="J42" s="42">
+        <v>4</v>
+      </c>
+      <c r="K42" s="42">
+        <v>4</v>
+      </c>
+      <c r="L42" s="42">
+        <v>2</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
       <c r="N42" s="42"/>
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
@@ -48118,7 +48612,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="93"/>
+      <c r="C44" s="93">
+        <f>2+2+4+1+15+8+312</f>
+        <v>344</v>
+      </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
     </row>
@@ -50147,12 +50644,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14">
+        <v>17</v>
+      </c>
+      <c r="F8" s="14">
+        <v>16</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>16</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -50164,12 +50671,18 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>5</v>
+      </c>
       <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -50335,12 +50848,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>6</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -50352,23 +50875,39 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>17</v>
+      </c>
+      <c r="F16" s="27">
+        <v>16</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>10</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -50380,10 +50919,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>5</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -50789,15 +51332,25 @@
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>38</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>8</v>
+      </c>
+      <c r="M24" s="14">
+        <v>434</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -50975,15 +51528,25 @@
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>24</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>7</v>
+      </c>
+      <c r="M31" s="23">
+        <v>96</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>87</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -51003,15 +51566,25 @@
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>14</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>1</v>
+      </c>
+      <c r="M32" s="28">
+        <v>338</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -51151,18 +51724,34 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="42">
+        <v>348</v>
+      </c>
+      <c r="G36" s="42">
+        <v>28</v>
+      </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
       <c r="K36" s="42"/>
       <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="M36" s="42">
+        <v>3</v>
+      </c>
+      <c r="N36" s="42">
+        <v>13</v>
+      </c>
+      <c r="O36" s="42">
+        <v>10</v>
+      </c>
+      <c r="P36" s="42">
+        <v>8</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>22</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -51309,18 +51898,34 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="F42" s="42">
+        <v>348</v>
+      </c>
+      <c r="G42" s="42">
+        <v>28</v>
+      </c>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="M42" s="42">
+        <v>3</v>
+      </c>
+      <c r="N42" s="42">
+        <v>13</v>
+      </c>
+      <c r="O42" s="42">
+        <v>10</v>
+      </c>
+      <c r="P42" s="42">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>22</v>
+      </c>
       <c r="R42" s="85" t="s">
         <v>54</v>
       </c>
@@ -51363,8 +51968,8 @@
         <v>68</v>
       </c>
       <c r="C44" s="93">
-        <f>1+1+26+15+15+3+5+62+2+10+551</f>
-        <v>691</v>
+        <f>17+16+10+5+14+1+338</f>
+        <v>401</v>
       </c>
       <c r="D44" s="93"/>
       <c r="E44" s="93"/>
